--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3313,6 +3313,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>07-Sep-2026  16:19:05</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3325,7 +3349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6572,6 +6596,34 @@
         <v>2</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="C116" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D116" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E116" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F116" s="9" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G116" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" s="11" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3337,6 +3337,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>08-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>08-Sep-2026  14:55:19</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="D117" s="4" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3349,7 +3373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6624,6 +6648,34 @@
         <v>0.6</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>08-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C117" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D117" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F117" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="G117" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H117" s="11" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3361,6 +3361,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>09-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>09-Sep-2026  15:04:11</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D118" s="12" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3373,7 +3397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6676,6 +6700,34 @@
         <v>2.4</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>09-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C118" s="6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D118" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F118" s="9" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H118" s="11" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3385,6 +3385,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>10-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>10-Sep-2026  14:49:35</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3397,7 +3421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6728,6 +6752,34 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>10-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="C119" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D119" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G119" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H119" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3409,6 +3409,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>11-Sep-2026  14:53:26</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D120" s="12" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3421,7 +3445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6780,6 +6804,34 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="C120" s="6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D120" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F120" s="9" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="G120" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H120" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3433,6 +3433,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>14-Sep-2026  16:49:26</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D121" s="12" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3445,7 +3469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6832,6 +6856,34 @@
         <v>1</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="C121" s="6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D121" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F121" s="9" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="G121" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H121" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3457,6 +3457,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>15-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>15-Sep-2026  15:29:21</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="D122" s="12" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3469,7 +3493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6884,6 +6908,34 @@
         <v>1</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>15-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="C122" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="D122" s="7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E122" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="9" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G122" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H122" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F122"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3481,6 +3481,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>16-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>16-Sep-2026  15:22:16</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="D123" s="12" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3493,7 +3517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6936,6 +6960,34 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>16-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="C123" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D123" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E123" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F123" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="G123" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H123" s="11" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3505,6 +3505,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>17-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>17-Sep-2026  15:28:35</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="D124" s="12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3517,7 +3541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H123"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6988,6 +7012,34 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>17-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="C124" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D124" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="9" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="G124" s="10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H124" s="11" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3529,6 +3529,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>18-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>18-Sep-2026  14:49:35</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="D125" s="12" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3541,7 +3565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7040,6 +7064,34 @@
         <v>1.8</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>18-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="C125" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D125" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F125" s="9" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="G125" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H125" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3553,6 +3553,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>21-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>21-Sep-2026  16:49:34</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="D126" s="12" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3565,7 +3589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7092,6 +7116,34 @@
         <v>8</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>21-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C126" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D126" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E126" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F126" s="9" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="G126" s="10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H126" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3577,6 +3577,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>22-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>22-Sep-2026  15:27:23</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="D127" s="12" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3589,7 +3613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7144,6 +7168,34 @@
         <v>2</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>22-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="C127" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D127" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F127" s="9" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G127" s="10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H127" s="11" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3601,6 +3601,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>23-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>23-Sep-2026  15:20:01</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="D128" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3613,7 +3637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7196,6 +7220,34 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>23-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="C128" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D128" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E128" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F128" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="G128" s="10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H128" s="11" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3625,6 +3625,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>24-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>24-Sep-2026  15:45:39</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D129" s="12" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3637,7 +3661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7248,6 +7272,34 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>24-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="C129" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D129" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F129" s="9" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G129" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H129" s="11" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3649,6 +3649,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>25-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>25-Sep-2026  15:46:31</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D130" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3661,7 +3685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7300,6 +7324,34 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>25-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="C130" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D130" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E130" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F130" s="9" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="G130" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H130" s="11" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3673,6 +3673,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>25-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>28-Sep-2026  18:27:13</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D131" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3685,7 +3709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7352,6 +7376,34 @@
         <v>0.6</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>25-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="C131" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D131" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="9" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G131" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" s="11" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3697,6 +3697,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>29-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>29-Sep-2026  16:49:54</t>
+        </is>
+      </c>
+      <c r="C132" s="12" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D132" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E132" s="12" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3709,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7404,6 +7428,34 @@
         <v>0.6</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>29-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="C132" s="6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D132" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F132" s="9" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G132" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H132" s="11" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3721,6 +3721,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>30-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>30-Sep-2026  16:42:18</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D133" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="E133" s="12" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3733,7 +3757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7456,6 +7480,34 @@
         <v>0.6</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>30-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="C133" s="6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D133" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F133" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="G133" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H133" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3745,6 +3745,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>01-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>01-Oct-2026  17:17:59</t>
+        </is>
+      </c>
+      <c r="C134" s="12" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D134" s="12" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="E134" s="12" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3757,7 +3781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7508,6 +7532,34 @@
         <v>2</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>01-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="C134" s="6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D134" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E134" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F134" s="9" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G134" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H134" s="11" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3769,6 +3769,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>01-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>02-Oct-2026  16:31:32</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D135" s="12" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="E135" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3781,7 +3805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7560,6 +7584,34 @@
         <v>0.6</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>01-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="C135" s="6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D135" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F135" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="G135" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H135" s="11" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3793,6 +3793,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>06-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>06-Oct-2026  17:05:47</t>
+        </is>
+      </c>
+      <c r="C136" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="D136" s="12" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E136" s="12" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3805,7 +3829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7612,6 +7636,34 @@
         <v>0.6</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>06-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="C136" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D136" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E136" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F136" s="9" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="G136" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H136" s="11" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3817,6 +3817,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>07-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>07-Oct-2026  17:43:10</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D137" s="12" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E137" s="12" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3829,7 +3853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7664,6 +7688,34 @@
         <v>3.4</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>07-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="C137" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D137" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F137" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="G137" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H137" s="11" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3841,6 +3841,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>08-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>08-Oct-2026  17:45:57</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="D138" s="12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E138" s="12" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3853,7 +3877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7716,6 +7740,34 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>08-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="C138" s="6" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D138" s="7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E138" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G138" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H138" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3865,6 +3865,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>09-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>09-Oct-2026  17:20:46</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D139" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="E139" s="12" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3877,7 +3901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7768,6 +7792,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>09-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C139" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D139" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="9" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="G139" s="10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H139" s="11" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3889,6 +3889,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>09-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>12-Oct-2026  20:09:29</t>
+        </is>
+      </c>
+      <c r="C140" s="12" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D140" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="E140" s="12" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3901,7 +3925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7820,6 +7844,34 @@
         <v>1.6</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>09-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="C140" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D140" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="9" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="G140" s="10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H140" s="11" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3913,6 +3913,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>13-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>13-Oct-2026  17:59:26</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D141" s="12" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E141" s="12" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3925,7 +3949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7872,6 +7896,34 @@
         <v>1.6</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>13-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C141" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D141" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="9" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="G141" s="10" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H141" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3937,6 +3937,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>14-Oct-2026  15:44:16</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="D142" s="12" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E142" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3949,7 +3973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7924,6 +7948,34 @@
         <v>8</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="C142" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D142" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E142" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="9" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G142" s="10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H142" s="11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3961,6 +3961,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>15-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>15-Oct-2026  15:32:30</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D143" s="12" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E143" s="12" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3973,7 +3997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H142"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7976,6 +8000,34 @@
         <v>2.8</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>15-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="C143" s="6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D143" s="7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F143" s="9" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="G143" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H143" s="11" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3985,6 +3985,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>16-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>16-Oct-2026  15:13:13</t>
+        </is>
+      </c>
+      <c r="C144" s="12" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="D144" s="12" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E144" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3997,7 +4021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8028,6 +8052,34 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>16-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="C144" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D144" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E144" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F144" s="9" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="G144" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H144" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4009,6 +4009,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>19-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>19-Oct-2026  17:22:04</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D145" s="12" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E145" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4021,7 +4045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8080,6 +8104,34 @@
         <v>1</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>19-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="C145" s="6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D145" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E145" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F145" s="9" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G145" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H145" s="11" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4033,6 +4033,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>19-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>20-Oct-2026  15:35:38</t>
+        </is>
+      </c>
+      <c r="C146" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D146" s="12" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E146" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4045,7 +4069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8132,6 +8156,34 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>19-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="C146" s="6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D146" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E146" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F146" s="9" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G146" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H146" s="11" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4057,6 +4057,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>21-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>21-Oct-2026  15:53:02</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="D147" s="12" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E147" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4069,7 +4093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8184,6 +8208,34 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>21-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="C147" s="6" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D147" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E147" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F147" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G147" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H147" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4081,6 +4081,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>22-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>22-Oct-2026  15:50:01</t>
+        </is>
+      </c>
+      <c r="C148" s="12" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D148" s="12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E148" s="12" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4093,7 +4117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8236,6 +8260,34 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>22-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="C148" s="6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D148" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E148" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F148" s="9" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G148" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" s="11" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4105,6 +4105,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>23-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>23-Oct-2026  15:40:52</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D149" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E149" s="12" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4117,7 +4141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8288,6 +8312,34 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>23-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="C149" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D149" s="7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E149" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G149" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H149" s="11" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4129,6 +4129,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-2026  17:10:40</t>
+        </is>
+      </c>
+      <c r="C150" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="D150" s="12" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E150" s="12" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4141,7 +4165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8340,6 +8364,34 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C150" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D150" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E150" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="9" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="G150" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H150" s="11" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4153,6 +4153,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>27-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>27-Oct-2026  16:14:05</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D151" s="12" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E151" s="12" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4165,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8392,6 +8416,34 @@
         <v>3.2</v>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>27-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C151" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D151" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E151" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="9" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="G151" s="10" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H151" s="11" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4177,6 +4177,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>28-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>28-Oct-2026  17:01:13</t>
+        </is>
+      </c>
+      <c r="C152" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D152" s="12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E152" s="12" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4189,7 +4213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8444,6 +8468,34 @@
         <v>6.2</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>28-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="C152" s="6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D152" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E152" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F152" s="9" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="G152" s="10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H152" s="11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4201,6 +4201,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>29-Oct-2026  17:21:25</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="D153" s="12" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E153" s="12" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4213,7 +4237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8496,6 +8520,34 @@
         <v>2.8</v>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C153" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D153" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F153" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="G153" s="10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H153" s="11" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4225,6 +4225,30 @@
         <v>500</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>30-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>30-Oct-2026  16:59:20</t>
+        </is>
+      </c>
+      <c r="C154" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D154" s="12" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="E154" s="12" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4237,7 +4261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8548,6 +8572,34 @@
         <v>3.8</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>30-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="C154" s="6" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D154" s="7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E154" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F154" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G154" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H154" s="11" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
